--- a/appium_test_analysis.xlsx
+++ b/appium_test_analysis.xlsx
@@ -494,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📱 Appium Mobile Test Automation Summary</t>
+          <t>Appium Mobile Test Automation Summary</t>
         </is>
       </c>
     </row>
